--- a/files/scripts/statistical_test_scripts/rq3_result/rq3_damping_sensitivity.xlsx
+++ b/files/scripts/statistical_test_scripts/rq3_result/rq3_damping_sensitivity.xlsx
@@ -977,7 +977,7 @@
       </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="n">
-        <v>1.351129504179664e-47</v>
+        <v>4.503765013932213e-48</v>
       </c>
       <c r="L12" t="b">
         <v>1</v>
@@ -1045,30 +1045,26 @@
         <v>400</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>83.88</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>91.91</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>800</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>all three damping levels identical</t>
-        </is>
-      </c>
+        <v>1.915169596713976e-174</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>1.532135677371181e-173</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -1091,23 +1087,23 @@
         <v>400</v>
       </c>
       <c r="E15" t="n">
-        <v>0.68</v>
+        <v>21.59</v>
       </c>
       <c r="F15" t="n">
-        <v>0.35</v>
+        <v>11.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.13</v>
+        <v>6.835</v>
       </c>
       <c r="H15" t="n">
-        <v>642.5389447236182</v>
+        <v>800</v>
       </c>
       <c r="I15" t="n">
-        <v>2.98154212226252e-140</v>
+        <v>1.915169596713976e-174</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>2.385233697810016e-139</v>
+        <v>1.532135677371181e-173</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -1133,7 +1129,7 @@
         <v>279</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>60.27</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
@@ -1142,21 +1138,17 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>520.1970021413274</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>all three damping levels identical</t>
-        </is>
-      </c>
+        <v>1.098136264299223e-113</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>4.39254505719689e-113</v>
       </c>
       <c r="L16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1179,23 +1171,23 @@
         <v>279</v>
       </c>
       <c r="E17" t="n">
-        <v>44.44</v>
+        <v>84.44</v>
       </c>
       <c r="F17" t="n">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="H17" t="n">
-        <v>554.0286738351256</v>
+        <v>556.0071684587815</v>
       </c>
       <c r="I17" t="n">
-        <v>4.945407334655669e-121</v>
+        <v>1.838981752183743e-121</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>1.978162933862268e-120</v>
+        <v>7.355927008734973e-121</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -3081,7 +3073,7 @@
         <v>6.008245801996849e-37</v>
       </c>
       <c r="L29" t="n">
-        <v>2.403298320798739e-36</v>
+        <v>2.059969989256062e-36</v>
       </c>
       <c r="M29" t="b">
         <v>1</v>
@@ -3264,7 +3256,7 @@
         <v>7.73167726073069e-20</v>
       </c>
       <c r="L32" t="n">
-        <v>9.278012712876828e-19</v>
+        <v>2.650860775107665e-19</v>
       </c>
       <c r="M32" t="b">
         <v>1</v>
@@ -3390,7 +3382,7 @@
         <v>7.73167726073069e-20</v>
       </c>
       <c r="L34" t="n">
-        <v>9.278012712876828e-19</v>
+        <v>2.650860775107665e-19</v>
       </c>
       <c r="M34" t="b">
         <v>1</v>
@@ -3619,44 +3611,40 @@
         <v>400</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>83.88</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>-9.629999999999995</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>2.375604198247023e-67</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>1.909790708080438e-66</v>
       </c>
       <c r="M38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5</v>
+        <v>0.1702375</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.85</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -3684,44 +3672,40 @@
         <v>400</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>83.88</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>91.91</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-8.149999999999991</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>1.909790708080438e-66</v>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5</v>
+        <v>0.209875</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -3749,44 +3733,40 @@
         <v>400</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>74.06999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>91.91</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-17.14999999999999</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2.38718789968921e-67</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>1.909790708080438e-66</v>
       </c>
       <c r="M40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5</v>
+        <v>0.01663125</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -3814,28 +3794,28 @@
         <v>400</v>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>21.59</v>
       </c>
       <c r="H41" t="n">
-        <v>0.35</v>
+        <v>11.9</v>
       </c>
       <c r="I41" t="n">
-        <v>0.34</v>
+        <v>9.959999999999999</v>
       </c>
       <c r="J41" t="n">
-        <v>11280</v>
+        <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>3.221060993290265e-35</v>
+        <v>2.710104335025235e-67</v>
       </c>
       <c r="L41" t="n">
-        <v>1.104363769128091e-34</v>
+        <v>2.168083468020188e-66</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>0.720178125</v>
+        <v>0.87573125</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -3875,28 +3855,28 @@
         <v>400</v>
       </c>
       <c r="G42" t="n">
-        <v>0.35</v>
+        <v>11.9</v>
       </c>
       <c r="H42" t="n">
-        <v>0.13</v>
+        <v>6.835</v>
       </c>
       <c r="I42" t="n">
-        <v>0.22</v>
+        <v>5.45</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>4.063089011719078e-67</v>
+        <v>2.694964435187877e-67</v>
       </c>
       <c r="L42" t="n">
-        <v>4.875706814062893e-66</v>
+        <v>2.168083468020188e-66</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.815175</v>
+        <v>0.88888125</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -3936,28 +3916,28 @@
         <v>400</v>
       </c>
       <c r="G43" t="n">
-        <v>0.68</v>
+        <v>21.59</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>6.835</v>
       </c>
       <c r="I43" t="n">
-        <v>0.67</v>
+        <v>14.685</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>9.280708616382478e-68</v>
+        <v>2.697488271739023e-67</v>
       </c>
       <c r="L43" t="n">
-        <v>2.227370067931795e-66</v>
+        <v>2.168083468020188e-66</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0.94065625</v>
+        <v>0.9975875</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -3997,44 +3977,40 @@
         <v>279</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>60.27</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>-39.73</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>1.0391257543949e-48</v>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.85</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4074,32 +4050,28 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>3.808776548310099e-18</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>1.14263296449303e-17</v>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.5</v>
+        <v>0.3261648745519714</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -4127,44 +4099,40 @@
         <v>279</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>60.27</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-39.73</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>1.0391257543949e-48</v>
       </c>
       <c r="M46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -4192,22 +4160,22 @@
         <v>279</v>
       </c>
       <c r="G47" t="n">
-        <v>44.44</v>
+        <v>84.44</v>
       </c>
       <c r="H47" t="n">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="I47" t="n">
-        <v>41.82</v>
+        <v>80.12</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.088088336126827e-47</v>
+        <v>3.857365572525656e-49</v>
       </c>
       <c r="L47" t="n">
-        <v>8.24254259098359e-47</v>
+        <v>1.729251166711678e-48</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -4253,28 +4221,28 @@
         <v>279</v>
       </c>
       <c r="G48" t="n">
-        <v>2.39</v>
+        <v>4.32</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9900000000000002</v>
+        <v>2.1</v>
       </c>
       <c r="J48" t="n">
-        <v>186</v>
+        <v>1</v>
       </c>
       <c r="K48" t="n">
-        <v>1.166640187738744e-46</v>
+        <v>4.323127916779195e-49</v>
       </c>
       <c r="L48" t="n">
-        <v>5.599872901145972e-46</v>
+        <v>1.729251166711678e-48</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8129713133181742</v>
+        <v>0.8331342094782955</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4314,22 +4282,22 @@
         <v>279</v>
       </c>
       <c r="G49" t="n">
-        <v>44.44</v>
+        <v>84.44</v>
       </c>
       <c r="H49" t="n">
-        <v>1.4</v>
+        <v>2.22</v>
       </c>
       <c r="I49" t="n">
-        <v>43.04</v>
+        <v>82.22</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1.373757098497265e-47</v>
+        <v>2.421094468115838e-49</v>
       </c>
       <c r="L49" t="n">
-        <v>8.24254259098359e-47</v>
+        <v>1.452656680869503e-48</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
@@ -4991,30 +4959,26 @@
         <v>400</v>
       </c>
       <c r="E14" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="F14" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>100</v>
+        <v>97.34</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>760.5979381443296</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>all three damping levels identical</t>
-        </is>
-      </c>
+        <v>6.890587603023053e-166</v>
+      </c>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="n">
-        <v>1</v>
+        <v>5.512470082418442e-165</v>
       </c>
       <c r="L14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
@@ -5037,23 +5001,23 @@
         <v>400</v>
       </c>
       <c r="E15" t="n">
-        <v>0.68</v>
+        <v>3</v>
       </c>
       <c r="F15" t="n">
-        <v>0.35</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
-        <v>0.13</v>
+        <v>0.91</v>
       </c>
       <c r="H15" t="n">
-        <v>642.5389447236182</v>
+        <v>780.5</v>
       </c>
       <c r="I15" t="n">
-        <v>2.98154212226252e-140</v>
+        <v>3.285325747062912e-170</v>
       </c>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="n">
-        <v>2.385233697810016e-139</v>
+        <v>2.62826059765033e-169</v>
       </c>
       <c r="L15" t="b">
         <v>1</v>
@@ -5079,7 +5043,7 @@
         <v>279</v>
       </c>
       <c r="E16" t="n">
-        <v>100</v>
+        <v>73.77</v>
       </c>
       <c r="F16" t="n">
         <v>100</v>
@@ -5088,21 +5052,17 @@
         <v>100</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>520.1970021413274</v>
       </c>
       <c r="I16" t="n">
-        <v>1</v>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>all three damping levels identical</t>
-        </is>
-      </c>
+        <v>1.098136264299223e-113</v>
+      </c>
+      <c r="J16" t="inlineStr"/>
       <c r="K16" t="n">
-        <v>1</v>
+        <v>4.39254505719689e-113</v>
       </c>
       <c r="L16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -5125,23 +5085,23 @@
         <v>279</v>
       </c>
       <c r="E17" t="n">
-        <v>44.44</v>
+        <v>68.89</v>
       </c>
       <c r="F17" t="n">
-        <v>2.39</v>
+        <v>3.53</v>
       </c>
       <c r="G17" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="H17" t="n">
-        <v>554.0286738351256</v>
+        <v>558</v>
       </c>
       <c r="I17" t="n">
-        <v>4.945407334655669e-121</v>
+        <v>6.789527457587031e-122</v>
       </c>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="n">
-        <v>1.978162933862268e-120</v>
+        <v>2.715810983034813e-121</v>
       </c>
       <c r="L17" t="b">
         <v>1</v>
@@ -7573,44 +7533,40 @@
         <v>400</v>
       </c>
       <c r="G38" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H38" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="I38" t="n">
-        <v>0</v>
+        <v>-3.810000000000002</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
       </c>
       <c r="K38" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="L38" t="n">
-        <v>1</v>
+        <v>2.864686062120656e-66</v>
       </c>
       <c r="M38" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N38" t="n">
-        <v>0.5</v>
+        <v>0.23016875</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.85</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -7638,44 +7594,40 @@
         <v>400</v>
       </c>
       <c r="G39" t="n">
-        <v>100</v>
+        <v>94.70999999999999</v>
       </c>
       <c r="H39" t="n">
-        <v>100</v>
+        <v>97.34</v>
       </c>
       <c r="I39" t="n">
-        <v>0</v>
+        <v>-2.5</v>
       </c>
       <c r="J39" t="n">
-        <v>0</v>
+        <v>230</v>
       </c>
       <c r="K39" t="n">
-        <v>1</v>
+        <v>1.190072414598313e-58</v>
       </c>
       <c r="L39" t="n">
-        <v>1</v>
+        <v>9.520579316786502e-58</v>
       </c>
       <c r="M39" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N39" t="n">
-        <v>0.5</v>
+        <v>0.286959375</v>
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -7703,44 +7655,40 @@
         <v>400</v>
       </c>
       <c r="G40" t="n">
-        <v>100</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="H40" t="n">
-        <v>100</v>
+        <v>97.34</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>-6.269999999999996</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="L40" t="n">
-        <v>1</v>
+        <v>2.864686062120656e-66</v>
       </c>
       <c r="M40" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N40" t="n">
-        <v>0.5</v>
+        <v>0.138275</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -7768,28 +7716,28 @@
         <v>400</v>
       </c>
       <c r="G41" t="n">
-        <v>0.68</v>
+        <v>3</v>
       </c>
       <c r="H41" t="n">
-        <v>0.35</v>
+        <v>1.9</v>
       </c>
       <c r="I41" t="n">
-        <v>0.34</v>
+        <v>1.24</v>
       </c>
       <c r="J41" t="n">
-        <v>10230</v>
+        <v>55</v>
       </c>
       <c r="K41" t="n">
-        <v>9.298749359253808e-38</v>
+        <v>3.992300256811342e-67</v>
       </c>
       <c r="L41" t="n">
-        <v>3.719499743701523e-37</v>
+        <v>3.193840205449073e-66</v>
       </c>
       <c r="M41" t="b">
         <v>1</v>
       </c>
       <c r="N41" t="n">
-        <v>0.720659375</v>
+        <v>0.861753125</v>
       </c>
       <c r="O41" t="inlineStr">
         <is>
@@ -7829,28 +7777,28 @@
         <v>400</v>
       </c>
       <c r="G42" t="n">
-        <v>0.35</v>
+        <v>1.9</v>
       </c>
       <c r="H42" t="n">
-        <v>0.13</v>
+        <v>0.91</v>
       </c>
       <c r="I42" t="n">
-        <v>0.22</v>
+        <v>0.82</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>4.063089011719078e-67</v>
+        <v>2.657460141340925e-67</v>
       </c>
       <c r="L42" t="n">
-        <v>4.875706814062893e-66</v>
+        <v>3.193840205449073e-66</v>
       </c>
       <c r="M42" t="b">
         <v>1</v>
       </c>
       <c r="N42" t="n">
-        <v>0.815175</v>
+        <v>0.90229375</v>
       </c>
       <c r="O42" t="inlineStr">
         <is>
@@ -7890,28 +7838,28 @@
         <v>400</v>
       </c>
       <c r="G43" t="n">
-        <v>0.68</v>
+        <v>3</v>
       </c>
       <c r="H43" t="n">
-        <v>0.13</v>
+        <v>0.91</v>
       </c>
       <c r="I43" t="n">
-        <v>0.67</v>
+        <v>1.93</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>9.280708616382478e-68</v>
+        <v>2.666435701364362e-67</v>
       </c>
       <c r="L43" t="n">
-        <v>2.227370067931795e-66</v>
+        <v>3.193840205449073e-66</v>
       </c>
       <c r="M43" t="b">
         <v>1</v>
       </c>
       <c r="N43" t="n">
-        <v>0.94065625</v>
+        <v>0.990246875</v>
       </c>
       <c r="O43" t="inlineStr">
         <is>
@@ -7951,44 +7899,40 @@
         <v>279</v>
       </c>
       <c r="G44" t="n">
-        <v>100</v>
+        <v>73.77</v>
       </c>
       <c r="H44" t="n">
         <v>100</v>
       </c>
       <c r="I44" t="n">
-        <v>0</v>
+        <v>-26.23</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>1</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L44" t="n">
-        <v>1</v>
+        <v>1.0391257543949e-48</v>
       </c>
       <c r="M44" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N44" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.85</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -8028,32 +7972,28 @@
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>1</v>
+        <v>3.787463357164768e-18</v>
       </c>
       <c r="L45" t="n">
-        <v>1</v>
+        <v>1.514985342865907e-17</v>
       </c>
       <c r="M45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.5</v>
+        <v>0.3261648745519714</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -8081,44 +8021,40 @@
         <v>279</v>
       </c>
       <c r="G46" t="n">
-        <v>100</v>
+        <v>73.77</v>
       </c>
       <c r="H46" t="n">
         <v>100</v>
       </c>
       <c r="I46" t="n">
-        <v>0</v>
+        <v>-26.23</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
       </c>
       <c r="K46" t="n">
-        <v>1</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L46" t="n">
-        <v>1</v>
+        <v>1.0391257543949e-48</v>
       </c>
       <c r="M46" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N46" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>large</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>tie</t>
-        </is>
-      </c>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>d=0.9</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -8146,22 +8082,22 @@
         <v>279</v>
       </c>
       <c r="G47" t="n">
-        <v>44.44</v>
+        <v>68.89</v>
       </c>
       <c r="H47" t="n">
-        <v>2.39</v>
+        <v>3.53</v>
       </c>
       <c r="I47" t="n">
-        <v>41.82</v>
+        <v>65.36</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>1.088088336126827e-47</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L47" t="n">
-        <v>8.24254259098359e-47</v>
+        <v>8.659381286624164e-49</v>
       </c>
       <c r="M47" t="b">
         <v>1</v>
@@ -8207,28 +8143,28 @@
         <v>279</v>
       </c>
       <c r="G48" t="n">
-        <v>2.39</v>
+        <v>3.53</v>
       </c>
       <c r="H48" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="I48" t="n">
-        <v>0.9900000000000002</v>
+        <v>1.72</v>
       </c>
       <c r="J48" t="n">
-        <v>186</v>
+        <v>0</v>
       </c>
       <c r="K48" t="n">
-        <v>1.166640187738744e-46</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L48" t="n">
-        <v>5.599872901145972e-46</v>
+        <v>8.659381286624164e-49</v>
       </c>
       <c r="M48" t="b">
         <v>1</v>
       </c>
       <c r="N48" t="n">
-        <v>0.8129713133181742</v>
+        <v>0.8462763839107925</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -8268,22 +8204,22 @@
         <v>279</v>
       </c>
       <c r="G49" t="n">
-        <v>44.44</v>
+        <v>68.89</v>
       </c>
       <c r="H49" t="n">
-        <v>1.4</v>
+        <v>1.81</v>
       </c>
       <c r="I49" t="n">
-        <v>43.04</v>
+        <v>67.08</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
       </c>
       <c r="K49" t="n">
-        <v>1.373757098497265e-47</v>
+        <v>2.164845321656041e-49</v>
       </c>
       <c r="L49" t="n">
-        <v>8.24254259098359e-47</v>
+        <v>8.659381286624164e-49</v>
       </c>
       <c r="M49" t="b">
         <v>1</v>
